--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104581_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104581_W14.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3655</v>
+        <v>4.7676</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0107</v>
+        <v>1.6385</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3548</v>
+        <v>3.1291</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9133</v>
+        <v>2.9135</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6232</v>
+        <v>1.6282</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2901</v>
+        <v>1.2853</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9846</v>
+        <v>2.9697</v>
       </c>
       <c r="K2" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0712</v>
+        <v>-0.0562</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2273</v>
+        <v>0.6249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1603</v>
+        <v>-0.193</v>
       </c>
       <c r="U2" t="n">
-        <v>1.067</v>
+        <v>0.8179</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9935</v>
+        <v>4.512</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1511</v>
+        <v>1.7713</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8425</v>
+        <v>2.7407</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6365</v>
+        <v>1.6385</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3651</v>
+        <v>0.3648</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2715</v>
+        <v>1.2737</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0787</v>
+        <v>1.063</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5578</v>
+        <v>0.5755</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1717</v>
+        <v>0.6946</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0212</v>
+        <v>-0.3324</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1505</v>
+        <v>1.027</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4308</v>
+        <v>0.599</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1037</v>
+        <v>0.8506</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5344</v>
+        <v>-0.2516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0683</v>
+        <v>0.498</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1876</v>
+        <v>-0.4137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2559</v>
+        <v>0.9116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0173</v>
+        <v>0.8716</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0173</v>
+        <v>0.2758</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.5958</v>
       </c>
       <c r="M4" t="n">
-        <v>0.051</v>
+        <v>-0.3736</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.205</v>
+        <v>-0.6895</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2559</v>
+        <v>0.3159</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0696</v>
+        <v>-0.1266</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>-0.021</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1905</v>
+        <v>-0.1057</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3778</v>
+        <v>0.4425</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6655</v>
+        <v>-0.1036</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2877</v>
+        <v>0.5462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.496</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4156</v>
+        <v>-0.184</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9116</v>
+        <v>0.2593</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8741</v>
+        <v>0.0172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2771</v>
+        <v>0.0172</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5971</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3781</v>
+        <v>0.0581</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6927</v>
+        <v>-0.2012</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>0.2593</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3451</v>
+        <v>0.0697</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.1209</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1364</v>
+        <v>0.1906</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4328</v>
+        <v>-0.1564</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4964</v>
+        <v>1.7617</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9292</v>
+        <v>-1.9181</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0796</v>
+        <v>-2.0734</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1703</v>
+        <v>-2.1658</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0906</v>
+        <v>0.0924</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1277</v>
+        <v>-0.1516</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6101</v>
+        <v>-0.628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.952</v>
+        <v>-1.9218</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4231</v>
+        <v>-0.1498</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0434</v>
+        <v>-0.7389</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6203</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6675</v>
+        <v>2.6522</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9761</v>
+        <v>-1.1587</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1974</v>
+        <v>-1.6206</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1734</v>
+        <v>0.4619</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6409</v>
+        <v>-0.4758</v>
       </c>
       <c r="H7" t="n">
-        <v>0.404</v>
+        <v>-0.7351</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0449</v>
+        <v>0.2593</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4875</v>
+        <v>-0.2036</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1992</v>
+        <v>-0.2036</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7117</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1284</v>
+        <v>-0.2722</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7953</v>
+        <v>-0.5315</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3331</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5456</v>
+        <v>-0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1785</v>
+        <v>-0.2788</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3672</v>
+        <v>0.0512</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0229</v>
+        <v>-1.197</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2316</v>
+        <v>-1.4338</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2087</v>
+        <v>0.2368</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1983</v>
+        <v>-1.2063</v>
       </c>
       <c r="H8" t="n">
-        <v>1.326</v>
+        <v>1.3296</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5243</v>
+        <v>-2.5358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1596</v>
+        <v>0.1274</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8226</v>
+        <v>2.8096</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3579</v>
+        <v>-1.3337</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6291</v>
+        <v>0.4645</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2571</v>
+        <v>-0.4231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8861</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2828</v>
+        <v>-1.2705</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.61</v>
+        <v>1.0032</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3272</v>
+        <v>-2.2737</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4771</v>
+        <v>-0.635</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.733</v>
+        <v>0.4076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2559</v>
+        <v>-1.0426</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1976</v>
+        <v>1.4739</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1976</v>
+        <v>2.1891</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2795</v>
+        <v>-2.1089</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5354</v>
+        <v>-1.7814</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>-0.3275</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.352</v>
+        <v>0.2554</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>0.0136</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0738</v>
+        <v>0.2418</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0308</v>
+        <v>-3.6048</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3377</v>
+        <v>-3.0403</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3068</v>
+        <v>-0.5644</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.4365</v>
+        <v>-0.3969</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.5093</v>
+        <v>0.1142</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9272</v>
+        <v>-0.511</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.5077</v>
+        <v>-0.4409</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9723</v>
+        <v>0.4309</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5354</v>
+        <v>-0.8718</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5371</v>
+        <v>-0.3168</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3918</v>
+        <v>0.3608</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3811</v>
+        <v>0.1092</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.747</v>
+        <v>-0.3232</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1281</v>
+        <v>0.4324</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4783</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1572</v>
+        <v>-3.7896</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7113</v>
+        <v>-1.8937</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4459</v>
+        <v>-1.896</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6743</v>
+        <v>-1.6793</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9726</v>
+        <v>0.9709</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6469</v>
+        <v>-2.6502</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4819</v>
+        <v>-0.5196</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0292</v>
+        <v>2.006</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.511</v>
+        <v>-2.5255</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1924</v>
+        <v>-1.1598</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0804</v>
+        <v>0.3042</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5172</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4367</v>
+        <v>0.9388</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1676</v>
+        <v>-3.9862</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4461</v>
+        <v>-5.0185</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7215</v>
+        <v>1.0323</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4083</v>
+        <v>-5.4302</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1008</v>
+        <v>-3.5042</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5091</v>
+        <v>-1.926</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4308</v>
+        <v>-4.5282</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4329</v>
+        <v>-2.9862</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8637</v>
+        <v>-1.542</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0224</v>
+        <v>-0.902</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3321</v>
+        <v>-0.518</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3546</v>
+        <v>-0.384</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4398</v>
+        <v>0.4228</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3073</v>
+        <v>0.8157</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>1.4764</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4433</v>
+        <v>-6.1611</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.1936</v>
+        <v>-6.9973</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7503</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6985</v>
+        <v>-2.7025</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.264</v>
+        <v>-2.266</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4345</v>
+        <v>-0.4365</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8918</v>
+        <v>-1.9148</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4759</v>
+        <v>-1.4898</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8066</v>
+        <v>-0.7877</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1155</v>
+        <v>0.1835</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6496</v>
+        <v>0.7134</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.3459</v>
+        <v>-11.0032</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.1129</v>
+        <v>-13.0825</v>
       </c>
       <c r="F14" t="n">
-        <v>1.767</v>
+        <v>2.0794</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.499399999999998</v>
+        <v>-9.4741</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.4881</v>
+        <v>-4.4535</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.0113</v>
+        <v>-5.020499999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.035699999999999</v>
+        <v>-1.2359</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7897</v>
+        <v>3.668499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.825099999999999</v>
+        <v>-4.9043</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.463800000000001</v>
+        <v>-8.238300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.277899999999999</v>
+        <v>-8.122</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1861</v>
+        <v>-0.1162000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.9392</v>
+        <v>-7.9672</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.4151</v>
+        <v>-20.4869</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2685</v>
+        <v>2.6248</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.3248</v>
+        <v>-3.975</v>
       </c>
       <c r="U14" t="n">
-        <v>6.5931</v>
+        <v>6.5999</v>
       </c>
       <c r="V14" t="n">
-        <v>3.824400000000001</v>
+        <v>3.813</v>
       </c>
       <c r="W14" t="n">
-        <v>12.6621</v>
+        <v>12.6152</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.837899999999999</v>
+        <v>-8.802099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3669</v>
+        <v>5.1329</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7048</v>
+        <v>4.4232</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6621</v>
+        <v>0.7097</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7689</v>
+        <v>2.7616</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5856</v>
+        <v>2.586</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1174</v>
+        <v>2.0859</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5155</v>
+        <v>0.4924</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6515</v>
+        <v>0.6757</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0348</v>
+        <v>-0.2009</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4657</v>
+        <v>-0.7019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5866</v>
+        <v>4.2927</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8709</v>
+        <v>1.1513</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7156</v>
+        <v>3.1414</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9077</v>
+        <v>4.8815</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3755</v>
+        <v>2.3507</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5322</v>
+        <v>2.5308</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8502</v>
+        <v>4.7939</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4003</v>
+        <v>3.357</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0575</v>
+        <v>0.0876</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6141</v>
+        <v>-0.8863</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.6695</v>
+        <v>-1.3175</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0553</v>
+        <v>0.4313</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.324</v>
+        <v>2.1638</v>
       </c>
       <c r="E17" t="n">
-        <v>1.565</v>
+        <v>1.0785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.759</v>
+        <v>1.0853</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4798</v>
+        <v>0.4786</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8556</v>
+        <v>0.8586</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3759</v>
+        <v>-0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1729</v>
+        <v>0.1611</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3069</v>
+        <v>0.3174</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1558</v>
+        <v>-0.3148</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2994</v>
+        <v>-0.1721</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4552</v>
+        <v>-0.1427</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5707</v>
+        <v>1.9688</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2321</v>
+        <v>0.1483</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3386</v>
+        <v>1.8205</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2143</v>
+        <v>0.1709</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3188</v>
+        <v>-0.0256</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5331</v>
+        <v>0.1965</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0176</v>
+        <v>0.1834</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3983</v>
+        <v>0.7649</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4159</v>
+        <v>-0.5816</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1967</v>
+        <v>-0.0125</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0795</v>
+        <v>-0.7906</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>0.778</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.441</v>
+        <v>-0.202</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3478</v>
+        <v>-0.6692</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0246</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4282</v>
+        <v>1.4336</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0508</v>
+        <v>0.327</v>
       </c>
       <c r="F19" t="n">
-        <v>1.479</v>
+        <v>1.1066</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1783</v>
+        <v>-0.2137</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0216</v>
+        <v>0.3242</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1999</v>
+        <v>-0.538</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2145</v>
+        <v>-0.0285</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7824</v>
+        <v>0.3964</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5679</v>
+        <v>-0.4249</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0362</v>
+        <v>-0.1852</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.0722</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7678</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7501</v>
+        <v>0.309</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9043</v>
+        <v>-0.2301</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1542</v>
+        <v>0.5391</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>2.0212</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1954</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5825</v>
+        <v>-1.365</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7779</v>
+        <v>1.9773</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8542999999999999</v>
+        <v>2.6298</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0995</v>
+        <v>1.3305</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2452</v>
+        <v>1.2994</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8767</v>
+        <v>1.9686</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6101</v>
+        <v>1.8196</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2666</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0224</v>
+        <v>0.6613</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4894</v>
+        <v>-0.4891</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5118</v>
+        <v>1.1504</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.9592</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1423</v>
+        <v>-0.2938</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1179</v>
+        <v>-0.8296</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2603</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.4652</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6795</v>
+        <v>-2.9693</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7466</v>
+        <v>3.4345</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6338</v>
+        <v>-0.86</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3436</v>
+        <v>-1.1027</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2902</v>
+        <v>0.2427</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9982</v>
+        <v>-0.904</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8489</v>
+        <v>-0.628</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1493</v>
+        <v>-0.276</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5053</v>
+        <v>-0.4747</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1409</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>2.5039</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8351</v>
+        <v>0.4147</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1825</v>
+        <v>-0.4718</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3475</v>
+        <v>0.8865</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8146</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9044</v>
+        <v>0.199</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0897</v>
+        <v>-1.0786</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8102</v>
+        <v>0.4621</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1545</v>
+        <v>0.873</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.4109</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9154</v>
+        <v>1.0053</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.492</v>
+        <v>0.9308</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4234</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1052</v>
+        <v>-0.5432</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6626</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7678</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4343</v>
+        <v>-0.0732</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5353</v>
+        <v>-0.5786</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9696</v>
+        <v>0.5053</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1075</v>
+        <v>-1.0155</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0873</v>
+        <v>-3.2723</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1948</v>
+        <v>2.2568</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4557</v>
+        <v>-1.796</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8715000000000001</v>
+        <v>-1.1437</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4158</v>
+        <v>-0.6523</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0097</v>
+        <v>-1.927</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9351</v>
+        <v>-0.4966</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>-1.4303</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.554</v>
+        <v>0.131</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0636</v>
+        <v>-0.6471</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>0.778</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2852</v>
+        <v>0.2067</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6956</v>
+        <v>-0.8901</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4104</v>
+        <v>1.0967</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0978</v>
+        <v>-1.8607</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0101</v>
+        <v>-1.8002</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0877</v>
+        <v>-0.0605</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1271</v>
+        <v>1.1316</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9885</v>
+        <v>0.9853</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2165</v>
+        <v>0.232</v>
       </c>
       <c r="N25" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6805</v>
+        <v>-0.446</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2934</v>
+        <v>0.2929</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.3458</v>
+        <v>12.1413</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7672</v>
+        <v>-2.0795</v>
       </c>
       <c r="F26" t="n">
-        <v>13.1128</v>
+        <v>14.2206</v>
       </c>
       <c r="G26" t="n">
-        <v>9.499300000000002</v>
+        <v>9.474000000000002</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4881</v>
+        <v>4.4535</v>
       </c>
       <c r="I26" t="n">
-        <v>5.011300000000001</v>
+        <v>5.020499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>8.463900000000001</v>
+        <v>8.238299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>8.277899999999999</v>
+        <v>8.122199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1860000000000002</v>
+        <v>0.1161000000000003</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0355</v>
+        <v>1.2357</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.7897</v>
+        <v>-3.6687</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8254</v>
+        <v>4.904300000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>7.9391</v>
+        <v>7.9671</v>
       </c>
       <c r="Q26" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R26" t="n">
-        <v>20.4149</v>
+        <v>20.4867</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.2684</v>
+        <v>-1.4866</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.5931</v>
+        <v>-6.5998</v>
       </c>
       <c r="U26" t="n">
-        <v>4.3248</v>
+        <v>5.1131</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.824199999999999</v>
+        <v>-3.813000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>8.837900000000001</v>
+        <v>8.802100000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-12.6621</v>
+        <v>-12.6151</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104581_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104581_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.802099999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104581_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-12.6151</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
